--- a/module_1-from_ai_model_to_ai_product/assignment_2-RAG/assignment2_evaluation.xlsx
+++ b/module_1-from_ai_model_to_ai_product/assignment_2-RAG/assignment2_evaluation.xlsx
@@ -1534,13 +1534,13 @@
       </c>
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="G68" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -2640,7 +2640,7 @@
         <v>0</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88">
